--- a/artfynd/A 6982-2023 artfynd.xlsx
+++ b/artfynd/A 6982-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6982-2023 artfynd.xlsx
+++ b/artfynd/A 6982-2023 artfynd.xlsx
@@ -13383,10 +13383,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121072431</v>
+        <v>121072436</v>
       </c>
       <c r="B115" t="n">
-        <v>90687</v>
+        <v>78598</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13399,21 +13399,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13423,10 +13423,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>545260</v>
+        <v>545298</v>
       </c>
       <c r="R115" t="n">
-        <v>7205422</v>
+        <v>7205342</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13495,10 +13495,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121072425</v>
+        <v>121072427</v>
       </c>
       <c r="B116" t="n">
-        <v>90687</v>
+        <v>78598</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13511,21 +13511,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13535,10 +13535,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>545264</v>
+        <v>545248</v>
       </c>
       <c r="R116" t="n">
-        <v>7205490</v>
+        <v>7205488</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13607,10 +13607,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121072436</v>
+        <v>121072431</v>
       </c>
       <c r="B117" t="n">
-        <v>78598</v>
+        <v>90687</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13623,21 +13623,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13647,10 +13647,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>545298</v>
+        <v>545260</v>
       </c>
       <c r="R117" t="n">
-        <v>7205342</v>
+        <v>7205422</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13719,10 +13719,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121072427</v>
+        <v>121072425</v>
       </c>
       <c r="B118" t="n">
-        <v>78598</v>
+        <v>90687</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13735,21 +13735,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13759,10 +13759,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>545248</v>
+        <v>545264</v>
       </c>
       <c r="R118" t="n">
-        <v>7205488</v>
+        <v>7205490</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 6982-2023 artfynd.xlsx
+++ b/artfynd/A 6982-2023 artfynd.xlsx
@@ -11699,10 +11699,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121072439</v>
+        <v>121072416</v>
       </c>
       <c r="B100" t="n">
-        <v>79679</v>
+        <v>79683</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11715,21 +11715,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>545359</v>
+        <v>545113</v>
       </c>
       <c r="R100" t="n">
-        <v>7205329</v>
+        <v>7205696</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11811,10 +11811,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121072428</v>
+        <v>121072425</v>
       </c>
       <c r="B101" t="n">
-        <v>91042</v>
+        <v>90697</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11823,25 +11823,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>545259</v>
+        <v>545264</v>
       </c>
       <c r="R101" t="n">
         <v>7205490</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11923,10 +11923,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121072426</v>
+        <v>121072433</v>
       </c>
       <c r="B102" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11939,38 +11939,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>545258</v>
+        <v>545259</v>
       </c>
       <c r="R102" t="n">
-        <v>7205490</v>
+        <v>7205420</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12002,7 +11998,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12012,7 +12008,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12039,10 +12035,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121072437</v>
+        <v>121072432</v>
       </c>
       <c r="B103" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12079,10 +12075,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>545330</v>
+        <v>545259</v>
       </c>
       <c r="R103" t="n">
-        <v>7205341</v>
+        <v>7205419</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12114,7 +12110,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12124,7 +12120,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12151,10 +12147,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121072424</v>
+        <v>121072439</v>
       </c>
       <c r="B104" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12167,21 +12163,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12191,10 +12187,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>545253</v>
+        <v>545359</v>
       </c>
       <c r="R104" t="n">
-        <v>7205532</v>
+        <v>7205329</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12226,7 +12222,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12236,7 +12232,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12263,10 +12259,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121072438</v>
+        <v>121072412</v>
       </c>
       <c r="B105" t="n">
-        <v>78598</v>
+        <v>79586</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12275,25 +12271,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12303,10 +12299,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>545330</v>
+        <v>545088</v>
       </c>
       <c r="R105" t="n">
-        <v>7205341</v>
+        <v>7205770</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12338,7 +12334,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12348,7 +12344,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12375,10 +12371,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121072413</v>
+        <v>121072418</v>
       </c>
       <c r="B106" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12391,21 +12387,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12415,10 +12411,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>545088</v>
+        <v>545117</v>
       </c>
       <c r="R106" t="n">
-        <v>7205770</v>
+        <v>7205692</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12450,7 +12446,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12460,7 +12456,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12487,10 +12483,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121072435</v>
+        <v>121072434</v>
       </c>
       <c r="B107" t="n">
-        <v>79680</v>
+        <v>57351</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12503,34 +12499,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>545302</v>
+        <v>545304</v>
       </c>
       <c r="R107" t="n">
-        <v>7205342</v>
+        <v>7205337</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12599,10 +12600,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121072429</v>
+        <v>121072435</v>
       </c>
       <c r="B108" t="n">
-        <v>90973</v>
+        <v>79683</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12615,21 +12616,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12639,10 +12640,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>545250</v>
+        <v>545302</v>
       </c>
       <c r="R108" t="n">
-        <v>7205496</v>
+        <v>7205342</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12674,7 +12675,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12684,7 +12685,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12711,10 +12712,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121072423</v>
+        <v>121072415</v>
       </c>
       <c r="B109" t="n">
-        <v>77982</v>
+        <v>78601</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12727,21 +12728,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12751,10 +12752,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>545255</v>
+        <v>545101</v>
       </c>
       <c r="R109" t="n">
-        <v>7205530</v>
+        <v>7205703</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12786,7 +12787,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12796,7 +12797,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12823,10 +12824,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121072420</v>
+        <v>121072429</v>
       </c>
       <c r="B110" t="n">
-        <v>79680</v>
+        <v>90983</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12839,21 +12840,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12863,10 +12864,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>545128</v>
+        <v>545250</v>
       </c>
       <c r="R110" t="n">
-        <v>7205649</v>
+        <v>7205496</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12898,7 +12899,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12908,7 +12909,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12935,10 +12936,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121072415</v>
+        <v>121072437</v>
       </c>
       <c r="B111" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12951,21 +12952,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12975,10 +12976,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>545101</v>
+        <v>545330</v>
       </c>
       <c r="R111" t="n">
-        <v>7205703</v>
+        <v>7205341</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13010,7 +13011,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13020,7 +13021,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13047,10 +13048,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121072433</v>
+        <v>121072436</v>
       </c>
       <c r="B112" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13087,10 +13088,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>545259</v>
+        <v>545298</v>
       </c>
       <c r="R112" t="n">
-        <v>7205420</v>
+        <v>7205342</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13122,7 +13123,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13132,7 +13133,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13159,10 +13160,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121072432</v>
+        <v>121072417</v>
       </c>
       <c r="B113" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13175,21 +13176,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13199,10 +13200,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>545259</v>
+        <v>545116</v>
       </c>
       <c r="R113" t="n">
-        <v>7205419</v>
+        <v>7205693</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13234,7 +13235,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13244,7 +13245,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13271,10 +13272,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121072416</v>
+        <v>121072420</v>
       </c>
       <c r="B114" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13311,10 +13312,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>545113</v>
+        <v>545128</v>
       </c>
       <c r="R114" t="n">
-        <v>7205696</v>
+        <v>7205649</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13346,7 +13347,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13356,7 +13357,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13383,10 +13384,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121072436</v>
+        <v>121072438</v>
       </c>
       <c r="B115" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13423,10 +13424,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>545298</v>
+        <v>545330</v>
       </c>
       <c r="R115" t="n">
-        <v>7205342</v>
+        <v>7205341</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13458,7 +13459,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13468,7 +13469,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13495,10 +13496,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121072427</v>
+        <v>121072414</v>
       </c>
       <c r="B116" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13511,21 +13512,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13535,10 +13536,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>545248</v>
+        <v>545093</v>
       </c>
       <c r="R116" t="n">
-        <v>7205488</v>
+        <v>7205711</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13570,7 +13571,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13580,7 +13581,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13607,10 +13608,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121072431</v>
+        <v>121072424</v>
       </c>
       <c r="B117" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13623,21 +13624,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13647,10 +13648,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>545260</v>
+        <v>545253</v>
       </c>
       <c r="R117" t="n">
-        <v>7205422</v>
+        <v>7205532</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13682,7 +13683,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13692,7 +13693,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13719,10 +13720,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121072425</v>
+        <v>121072430</v>
       </c>
       <c r="B118" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13735,21 +13736,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13759,10 +13760,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>545264</v>
+        <v>545250</v>
       </c>
       <c r="R118" t="n">
-        <v>7205490</v>
+        <v>7205496</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13794,7 +13795,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13804,7 +13805,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13831,10 +13832,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121072434</v>
+        <v>121072413</v>
       </c>
       <c r="B119" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13847,39 +13848,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>545304</v>
+        <v>545088</v>
       </c>
       <c r="R119" t="n">
-        <v>7205337</v>
+        <v>7205770</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13911,7 +13907,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13921,7 +13917,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13948,10 +13944,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121072412</v>
+        <v>121072428</v>
       </c>
       <c r="B120" t="n">
-        <v>79583</v>
+        <v>91052</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13960,25 +13956,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6456</v>
+        <v>1506</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13988,10 +13984,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>545088</v>
+        <v>545259</v>
       </c>
       <c r="R120" t="n">
-        <v>7205770</v>
+        <v>7205490</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14023,7 +14019,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14033,7 +14029,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14060,10 +14056,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121072417</v>
+        <v>121072440</v>
       </c>
       <c r="B121" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14100,10 +14096,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>545116</v>
+        <v>545358</v>
       </c>
       <c r="R121" t="n">
-        <v>7205693</v>
+        <v>7205334</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14135,7 +14131,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14145,7 +14141,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14172,10 +14168,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121072418</v>
+        <v>121072421</v>
       </c>
       <c r="B122" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14188,21 +14184,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14212,10 +14208,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>545117</v>
+        <v>545129</v>
       </c>
       <c r="R122" t="n">
-        <v>7205692</v>
+        <v>7205646</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14247,7 +14243,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14257,7 +14253,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14284,10 +14280,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121072430</v>
+        <v>121072431</v>
       </c>
       <c r="B123" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14300,21 +14296,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14324,10 +14320,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>545250</v>
+        <v>545260</v>
       </c>
       <c r="R123" t="n">
-        <v>7205496</v>
+        <v>7205422</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14359,7 +14355,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14369,7 +14365,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14396,10 +14392,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121072440</v>
+        <v>121072423</v>
       </c>
       <c r="B124" t="n">
-        <v>78598</v>
+        <v>77985</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14412,21 +14408,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14436,10 +14432,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>545358</v>
+        <v>545255</v>
       </c>
       <c r="R124" t="n">
-        <v>7205334</v>
+        <v>7205530</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14471,7 +14467,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14481,7 +14477,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14508,10 +14504,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121072421</v>
+        <v>121072427</v>
       </c>
       <c r="B125" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14548,10 +14544,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>545129</v>
+        <v>545248</v>
       </c>
       <c r="R125" t="n">
-        <v>7205646</v>
+        <v>7205488</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14583,7 +14579,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14593,7 +14589,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14620,10 +14616,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121072414</v>
+        <v>121072426</v>
       </c>
       <c r="B126" t="n">
-        <v>90705</v>
+        <v>57504</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14636,34 +14632,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>545093</v>
+        <v>545258</v>
       </c>
       <c r="R126" t="n">
-        <v>7205711</v>
+        <v>7205490</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 6982-2023 artfynd.xlsx
+++ b/artfynd/A 6982-2023 artfynd.xlsx
@@ -11699,10 +11699,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121072416</v>
+        <v>121072414</v>
       </c>
       <c r="B100" t="n">
-        <v>79683</v>
+        <v>90715</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11715,21 +11715,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>545113</v>
+        <v>545093</v>
       </c>
       <c r="R100" t="n">
-        <v>7205696</v>
+        <v>7205711</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11811,10 +11811,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121072425</v>
+        <v>121072420</v>
       </c>
       <c r="B101" t="n">
-        <v>90697</v>
+        <v>79683</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11827,21 +11827,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>545264</v>
+        <v>545128</v>
       </c>
       <c r="R101" t="n">
-        <v>7205490</v>
+        <v>7205649</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11923,10 +11923,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121072433</v>
+        <v>121072435</v>
       </c>
       <c r="B102" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11939,21 +11939,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>545259</v>
+        <v>545302</v>
       </c>
       <c r="R102" t="n">
-        <v>7205420</v>
+        <v>7205342</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12035,10 +12035,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121072432</v>
+        <v>121072423</v>
       </c>
       <c r="B103" t="n">
-        <v>79683</v>
+        <v>77985</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12051,21 +12051,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>545259</v>
+        <v>545255</v>
       </c>
       <c r="R103" t="n">
-        <v>7205419</v>
+        <v>7205530</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12147,10 +12147,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121072439</v>
+        <v>121072426</v>
       </c>
       <c r="B104" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12163,34 +12163,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>545359</v>
+        <v>545258</v>
       </c>
       <c r="R104" t="n">
-        <v>7205329</v>
+        <v>7205490</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12222,7 +12226,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12232,7 +12236,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12259,10 +12263,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121072412</v>
+        <v>121072416</v>
       </c>
       <c r="B105" t="n">
-        <v>79586</v>
+        <v>79683</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12271,25 +12275,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12299,10 +12303,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>545088</v>
+        <v>545113</v>
       </c>
       <c r="R105" t="n">
-        <v>7205770</v>
+        <v>7205696</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12334,7 +12338,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12344,7 +12348,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12371,10 +12375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121072418</v>
+        <v>121072425</v>
       </c>
       <c r="B106" t="n">
-        <v>79683</v>
+        <v>90697</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12387,21 +12391,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12411,10 +12415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>545117</v>
+        <v>545264</v>
       </c>
       <c r="R106" t="n">
-        <v>7205692</v>
+        <v>7205490</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12446,7 +12450,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12456,7 +12460,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12483,10 +12487,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121072434</v>
+        <v>121072432</v>
       </c>
       <c r="B107" t="n">
-        <v>57351</v>
+        <v>79683</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12499,39 +12503,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>545304</v>
+        <v>545259</v>
       </c>
       <c r="R107" t="n">
-        <v>7205337</v>
+        <v>7205419</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12563,7 +12562,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12573,7 +12572,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12600,10 +12599,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121072435</v>
+        <v>121072421</v>
       </c>
       <c r="B108" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12616,21 +12615,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12640,10 +12639,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>545302</v>
+        <v>545129</v>
       </c>
       <c r="R108" t="n">
-        <v>7205342</v>
+        <v>7205646</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12675,7 +12674,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12685,7 +12684,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12712,7 +12711,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121072415</v>
+        <v>121072417</v>
       </c>
       <c r="B109" t="n">
         <v>78601</v>
@@ -12752,10 +12751,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>545101</v>
+        <v>545116</v>
       </c>
       <c r="R109" t="n">
-        <v>7205703</v>
+        <v>7205693</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12787,7 +12786,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12797,7 +12796,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12824,10 +12823,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121072429</v>
+        <v>121072439</v>
       </c>
       <c r="B110" t="n">
-        <v>90983</v>
+        <v>79682</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12840,21 +12839,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12864,10 +12863,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>545250</v>
+        <v>545359</v>
       </c>
       <c r="R110" t="n">
-        <v>7205496</v>
+        <v>7205329</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12899,7 +12898,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12909,7 +12908,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12936,10 +12935,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121072437</v>
+        <v>121072433</v>
       </c>
       <c r="B111" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12952,21 +12951,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12976,10 +12975,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>545330</v>
+        <v>545259</v>
       </c>
       <c r="R111" t="n">
-        <v>7205341</v>
+        <v>7205420</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13011,7 +13010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13021,7 +13020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13048,10 +13047,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121072436</v>
+        <v>121072418</v>
       </c>
       <c r="B112" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13064,21 +13063,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13088,10 +13087,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>545298</v>
+        <v>545117</v>
       </c>
       <c r="R112" t="n">
-        <v>7205342</v>
+        <v>7205692</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13123,7 +13122,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13133,7 +13132,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13160,10 +13159,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121072417</v>
+        <v>121072431</v>
       </c>
       <c r="B113" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13176,21 +13175,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13200,10 +13199,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>545116</v>
+        <v>545260</v>
       </c>
       <c r="R113" t="n">
-        <v>7205693</v>
+        <v>7205422</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13235,7 +13234,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13245,7 +13244,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13272,10 +13271,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121072420</v>
+        <v>121072430</v>
       </c>
       <c r="B114" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13288,21 +13287,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13312,10 +13311,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>545128</v>
+        <v>545250</v>
       </c>
       <c r="R114" t="n">
-        <v>7205649</v>
+        <v>7205496</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13347,7 +13346,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13357,7 +13356,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13384,7 +13383,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121072438</v>
+        <v>121072436</v>
       </c>
       <c r="B115" t="n">
         <v>78601</v>
@@ -13424,10 +13423,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>545330</v>
+        <v>545298</v>
       </c>
       <c r="R115" t="n">
-        <v>7205341</v>
+        <v>7205342</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13459,7 +13458,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13469,7 +13468,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13496,10 +13495,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121072414</v>
+        <v>121072428</v>
       </c>
       <c r="B116" t="n">
-        <v>90715</v>
+        <v>91052</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13508,25 +13507,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13536,10 +13535,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>545093</v>
+        <v>545259</v>
       </c>
       <c r="R116" t="n">
-        <v>7205711</v>
+        <v>7205490</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13571,7 +13570,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13581,7 +13580,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13608,7 +13607,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121072424</v>
+        <v>121072438</v>
       </c>
       <c r="B117" t="n">
         <v>78601</v>
@@ -13648,10 +13647,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>545253</v>
+        <v>545330</v>
       </c>
       <c r="R117" t="n">
-        <v>7205532</v>
+        <v>7205341</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13683,7 +13682,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13693,7 +13692,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13720,7 +13719,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121072430</v>
+        <v>121072440</v>
       </c>
       <c r="B118" t="n">
         <v>78601</v>
@@ -13760,10 +13759,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>545250</v>
+        <v>545358</v>
       </c>
       <c r="R118" t="n">
-        <v>7205496</v>
+        <v>7205334</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13795,7 +13794,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13805,7 +13804,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13832,7 +13831,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121072413</v>
+        <v>121072424</v>
       </c>
       <c r="B119" t="n">
         <v>78601</v>
@@ -13872,10 +13871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>545088</v>
+        <v>545253</v>
       </c>
       <c r="R119" t="n">
-        <v>7205770</v>
+        <v>7205532</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13907,7 +13906,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13917,7 +13916,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13944,10 +13943,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121072428</v>
+        <v>121072437</v>
       </c>
       <c r="B120" t="n">
-        <v>91052</v>
+        <v>79683</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13956,25 +13955,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1506</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13984,10 +13983,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>545259</v>
+        <v>545330</v>
       </c>
       <c r="R120" t="n">
-        <v>7205490</v>
+        <v>7205341</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14019,7 +14018,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14029,7 +14028,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14056,7 +14055,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121072440</v>
+        <v>121072415</v>
       </c>
       <c r="B121" t="n">
         <v>78601</v>
@@ -14096,10 +14095,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>545358</v>
+        <v>545101</v>
       </c>
       <c r="R121" t="n">
-        <v>7205334</v>
+        <v>7205703</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14131,7 +14130,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14141,7 +14140,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14168,7 +14167,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121072421</v>
+        <v>121072413</v>
       </c>
       <c r="B122" t="n">
         <v>78601</v>
@@ -14208,10 +14207,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>545129</v>
+        <v>545088</v>
       </c>
       <c r="R122" t="n">
-        <v>7205646</v>
+        <v>7205770</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14243,7 +14242,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14253,7 +14252,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14280,10 +14279,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121072431</v>
+        <v>121072429</v>
       </c>
       <c r="B123" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14296,21 +14295,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14320,10 +14319,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>545260</v>
+        <v>545250</v>
       </c>
       <c r="R123" t="n">
-        <v>7205422</v>
+        <v>7205496</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14355,7 +14354,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14365,7 +14364,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14392,10 +14391,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121072423</v>
+        <v>121072412</v>
       </c>
       <c r="B124" t="n">
-        <v>77985</v>
+        <v>79586</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14404,25 +14403,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14432,10 +14431,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>545255</v>
+        <v>545088</v>
       </c>
       <c r="R124" t="n">
-        <v>7205530</v>
+        <v>7205770</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14467,7 +14466,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14477,7 +14476,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14616,10 +14615,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121072426</v>
+        <v>121072434</v>
       </c>
       <c r="B126" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14632,26 +14631,27 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14660,10 +14660,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>545258</v>
+        <v>545304</v>
       </c>
       <c r="R126" t="n">
-        <v>7205490</v>
+        <v>7205337</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 6982-2023 artfynd.xlsx
+++ b/artfynd/A 6982-2023 artfynd.xlsx
@@ -12263,10 +12263,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121072416</v>
+        <v>121072425</v>
       </c>
       <c r="B105" t="n">
-        <v>79683</v>
+        <v>90697</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12279,21 +12279,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12303,10 +12303,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>545113</v>
+        <v>545264</v>
       </c>
       <c r="R105" t="n">
-        <v>7205696</v>
+        <v>7205490</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12375,10 +12375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121072425</v>
+        <v>121072416</v>
       </c>
       <c r="B106" t="n">
-        <v>90697</v>
+        <v>79683</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>545264</v>
+        <v>545113</v>
       </c>
       <c r="R106" t="n">
-        <v>7205490</v>
+        <v>7205696</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13943,10 +13943,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121072437</v>
+        <v>121072415</v>
       </c>
       <c r="B120" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13959,21 +13959,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13983,10 +13983,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>545330</v>
+        <v>545101</v>
       </c>
       <c r="R120" t="n">
-        <v>7205341</v>
+        <v>7205703</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14055,7 +14055,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121072415</v>
+        <v>121072413</v>
       </c>
       <c r="B121" t="n">
         <v>78601</v>
@@ -14095,10 +14095,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>545101</v>
+        <v>545088</v>
       </c>
       <c r="R121" t="n">
-        <v>7205703</v>
+        <v>7205770</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14167,10 +14167,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121072413</v>
+        <v>121072429</v>
       </c>
       <c r="B122" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14183,21 +14183,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14207,10 +14207,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>545088</v>
+        <v>545250</v>
       </c>
       <c r="R122" t="n">
-        <v>7205770</v>
+        <v>7205496</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14279,10 +14279,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121072429</v>
+        <v>121072437</v>
       </c>
       <c r="B123" t="n">
-        <v>90983</v>
+        <v>79683</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14295,21 +14295,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14319,10 +14319,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>545250</v>
+        <v>545330</v>
       </c>
       <c r="R123" t="n">
-        <v>7205496</v>
+        <v>7205341</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 6982-2023 artfynd.xlsx
+++ b/artfynd/A 6982-2023 artfynd.xlsx
@@ -11699,10 +11699,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121072414</v>
+        <v>121072418</v>
       </c>
       <c r="B100" t="n">
-        <v>90715</v>
+        <v>79686</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11715,21 +11715,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>545093</v>
+        <v>545117</v>
       </c>
       <c r="R100" t="n">
-        <v>7205711</v>
+        <v>7205692</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11811,10 +11811,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121072420</v>
+        <v>121072438</v>
       </c>
       <c r="B101" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11827,21 +11827,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>545128</v>
+        <v>545330</v>
       </c>
       <c r="R101" t="n">
-        <v>7205649</v>
+        <v>7205341</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11923,10 +11923,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121072435</v>
+        <v>121072430</v>
       </c>
       <c r="B102" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11939,21 +11939,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>545302</v>
+        <v>545250</v>
       </c>
       <c r="R102" t="n">
-        <v>7205342</v>
+        <v>7205496</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12035,10 +12035,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121072423</v>
+        <v>121072427</v>
       </c>
       <c r="B103" t="n">
-        <v>77985</v>
+        <v>78604</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12051,21 +12051,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>545255</v>
+        <v>545248</v>
       </c>
       <c r="R103" t="n">
-        <v>7205530</v>
+        <v>7205488</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12147,10 +12147,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121072426</v>
+        <v>121072434</v>
       </c>
       <c r="B104" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12163,26 +12163,27 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12191,10 +12192,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>545258</v>
+        <v>545304</v>
       </c>
       <c r="R104" t="n">
-        <v>7205490</v>
+        <v>7205337</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12226,7 +12227,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12236,7 +12237,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12263,10 +12264,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121072425</v>
+        <v>121072432</v>
       </c>
       <c r="B105" t="n">
-        <v>90697</v>
+        <v>79686</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12279,21 +12280,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12303,10 +12304,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>545264</v>
+        <v>545259</v>
       </c>
       <c r="R105" t="n">
-        <v>7205490</v>
+        <v>7205419</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12338,7 +12339,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12348,7 +12349,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12375,10 +12376,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121072416</v>
+        <v>121072437</v>
       </c>
       <c r="B106" t="n">
-        <v>79683</v>
+        <v>79686</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12415,10 +12416,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>545113</v>
+        <v>545330</v>
       </c>
       <c r="R106" t="n">
-        <v>7205696</v>
+        <v>7205341</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12450,7 +12451,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12460,7 +12461,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12487,10 +12488,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121072432</v>
+        <v>121072440</v>
       </c>
       <c r="B107" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12503,21 +12504,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12527,10 +12528,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>545259</v>
+        <v>545358</v>
       </c>
       <c r="R107" t="n">
-        <v>7205419</v>
+        <v>7205334</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12562,7 +12563,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12572,7 +12573,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12599,10 +12600,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121072421</v>
+        <v>121072420</v>
       </c>
       <c r="B108" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12615,21 +12616,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12639,10 +12640,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>545129</v>
+        <v>545128</v>
       </c>
       <c r="R108" t="n">
-        <v>7205646</v>
+        <v>7205649</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12711,10 +12712,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121072417</v>
+        <v>121072429</v>
       </c>
       <c r="B109" t="n">
-        <v>78601</v>
+        <v>90995</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12727,21 +12728,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12751,10 +12752,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>545116</v>
+        <v>545250</v>
       </c>
       <c r="R109" t="n">
-        <v>7205693</v>
+        <v>7205496</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12786,7 +12787,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12796,7 +12797,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12823,10 +12824,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121072439</v>
+        <v>121072421</v>
       </c>
       <c r="B110" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12839,21 +12840,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12863,10 +12864,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>545359</v>
+        <v>545129</v>
       </c>
       <c r="R110" t="n">
-        <v>7205329</v>
+        <v>7205646</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12898,7 +12899,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12908,7 +12909,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12935,10 +12936,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121072433</v>
+        <v>121072439</v>
       </c>
       <c r="B111" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12951,21 +12952,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12975,10 +12976,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>545259</v>
+        <v>545359</v>
       </c>
       <c r="R111" t="n">
-        <v>7205420</v>
+        <v>7205329</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13010,7 +13011,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13020,7 +13021,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13047,10 +13048,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121072418</v>
+        <v>121072425</v>
       </c>
       <c r="B112" t="n">
-        <v>79683</v>
+        <v>90709</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13063,21 +13064,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13087,10 +13088,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>545117</v>
+        <v>545264</v>
       </c>
       <c r="R112" t="n">
-        <v>7205692</v>
+        <v>7205490</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13122,7 +13123,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13132,7 +13133,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13159,10 +13160,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121072431</v>
+        <v>121072426</v>
       </c>
       <c r="B113" t="n">
-        <v>90697</v>
+        <v>57504</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13175,34 +13176,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>545260</v>
+        <v>545258</v>
       </c>
       <c r="R113" t="n">
-        <v>7205422</v>
+        <v>7205490</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13234,7 +13239,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13244,7 +13249,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13271,10 +13276,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121072430</v>
+        <v>121072435</v>
       </c>
       <c r="B114" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13287,21 +13292,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13311,10 +13316,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>545250</v>
+        <v>545302</v>
       </c>
       <c r="R114" t="n">
-        <v>7205496</v>
+        <v>7205342</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13346,7 +13351,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13356,7 +13361,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13383,10 +13388,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121072436</v>
+        <v>121072414</v>
       </c>
       <c r="B115" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13399,21 +13404,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13423,10 +13428,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>545298</v>
+        <v>545093</v>
       </c>
       <c r="R115" t="n">
-        <v>7205342</v>
+        <v>7205711</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13458,7 +13463,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13468,7 +13473,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13498,7 +13503,7 @@
         <v>121072428</v>
       </c>
       <c r="B116" t="n">
-        <v>91052</v>
+        <v>91064</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13607,10 +13612,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121072438</v>
+        <v>121072424</v>
       </c>
       <c r="B117" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13647,10 +13652,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>545330</v>
+        <v>545253</v>
       </c>
       <c r="R117" t="n">
-        <v>7205341</v>
+        <v>7205532</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13682,7 +13687,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13692,7 +13697,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13719,10 +13724,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121072440</v>
+        <v>121072415</v>
       </c>
       <c r="B118" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13759,10 +13764,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>545358</v>
+        <v>545101</v>
       </c>
       <c r="R118" t="n">
-        <v>7205334</v>
+        <v>7205703</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13794,7 +13799,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13804,7 +13809,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13831,10 +13836,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121072424</v>
+        <v>121072436</v>
       </c>
       <c r="B119" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13871,10 +13876,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>545253</v>
+        <v>545298</v>
       </c>
       <c r="R119" t="n">
-        <v>7205532</v>
+        <v>7205342</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13906,7 +13911,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13916,7 +13921,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13943,10 +13948,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121072415</v>
+        <v>121072433</v>
       </c>
       <c r="B120" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13983,10 +13988,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>545101</v>
+        <v>545259</v>
       </c>
       <c r="R120" t="n">
-        <v>7205703</v>
+        <v>7205420</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14018,7 +14023,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14028,7 +14033,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14055,10 +14060,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121072413</v>
+        <v>121072417</v>
       </c>
       <c r="B121" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14095,10 +14100,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>545088</v>
+        <v>545116</v>
       </c>
       <c r="R121" t="n">
-        <v>7205770</v>
+        <v>7205693</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14130,7 +14135,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14140,7 +14145,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14167,10 +14172,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121072429</v>
+        <v>121072413</v>
       </c>
       <c r="B122" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14183,21 +14188,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14207,10 +14212,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>545250</v>
+        <v>545088</v>
       </c>
       <c r="R122" t="n">
-        <v>7205496</v>
+        <v>7205770</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14242,7 +14247,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14252,7 +14257,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14279,10 +14284,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121072437</v>
+        <v>121072416</v>
       </c>
       <c r="B123" t="n">
-        <v>79683</v>
+        <v>79686</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14319,10 +14324,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>545330</v>
+        <v>545113</v>
       </c>
       <c r="R123" t="n">
-        <v>7205341</v>
+        <v>7205696</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14354,7 +14359,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14364,7 +14369,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14391,10 +14396,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121072412</v>
+        <v>121072431</v>
       </c>
       <c r="B124" t="n">
-        <v>79586</v>
+        <v>90709</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14403,25 +14408,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14431,10 +14436,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>545088</v>
+        <v>545260</v>
       </c>
       <c r="R124" t="n">
-        <v>7205770</v>
+        <v>7205422</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14466,7 +14471,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14476,7 +14481,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14503,10 +14508,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121072427</v>
+        <v>121072412</v>
       </c>
       <c r="B125" t="n">
-        <v>78601</v>
+        <v>79589</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14515,25 +14520,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14543,10 +14548,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>545248</v>
+        <v>545088</v>
       </c>
       <c r="R125" t="n">
-        <v>7205488</v>
+        <v>7205770</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14578,7 +14583,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14588,7 +14593,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14615,10 +14620,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121072434</v>
+        <v>121072423</v>
       </c>
       <c r="B126" t="n">
-        <v>57351</v>
+        <v>77988</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14631,39 +14636,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>545304</v>
+        <v>545255</v>
       </c>
       <c r="R126" t="n">
-        <v>7205337</v>
+        <v>7205530</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD126" t="b">
